--- a/InputData/elec/HOC/HOC Hydro Opportunity Costs.xlsx
+++ b/InputData/elec/HOC/HOC Hydro Opportunity Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\HOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\HOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F45B545-2B5C-4709-A9B3-53A6EDF8F65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68D914E-48BA-4FD1-B8AF-74A2C165F99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" activeTab="1" xr2:uid="{8AA2DA0F-B30C-412A-A55D-748BA994FC4B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{8AA2DA0F-B30C-412A-A55D-748BA994FC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +174,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -280,7 +280,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,7 +422,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -505,7 +505,7 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/HOC/HOC Hydro Opportunity Costs.xlsx
+++ b/InputData/elec/HOC/HOC Hydro Opportunity Costs.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27528"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\HOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\HOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68D914E-48BA-4FD1-B8AF-74A2C165F99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F45B545-2B5C-4709-A9B3-53A6EDF8F65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{8AA2DA0F-B30C-412A-A55D-748BA994FC4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" firstSheet="1" activeTab="1" xr2:uid="{8AA2DA0F-B30C-412A-A55D-748BA994FC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="HOC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -76,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,9 +137,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +177,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -280,7 +283,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,7 +425,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -431,14 +434,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7655D3-EAD7-4119-BC82-55DAF4FF9FE5}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -446,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -454,27 +457,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -490,25 +493,186 @@
     <tabColor theme="3" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B5FD6B-21D2-418E-872C-854C17075D83}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6095F90-A1F8-4454-9F2E-9D56D7699829}"/>
 </file>